--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,130 +26,94 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
   </x:si>
   <x:si>
     <x:t>EUKYO</x:t>
   </x:si>
   <x:si>
-    <x:t>HUNER</x:t>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
   </x:si>
   <x:si>
     <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
     <x:t>METRO</x:t>
   </x:si>
   <x:si>
-    <x:t>PETKM</x:t>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
   </x:si>
   <x:si>
     <x:t>SKYMD</x:t>
@@ -170,19 +134,10 @@
     <x:t>TRCAS</x:t>
   </x:si>
   <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
     <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKBN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -533,7 +488,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C8"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -555,72 +510,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:3">
-      <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:3">
-      <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:3">
-      <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -638,7 +527,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C45"/>
+  <x:dimension ref="A1:C36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -654,7 +543,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -665,7 +554,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -676,7 +565,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -687,7 +576,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -698,7 +587,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -709,7 +598,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -720,7 +609,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -731,7 +620,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -742,7 +631,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -753,7 +642,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -764,7 +653,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -775,7 +664,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -786,7 +675,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -797,7 +686,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -808,7 +697,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -819,7 +708,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -830,7 +719,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -841,7 +730,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -852,7 +741,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -863,7 +752,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -874,7 +763,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -885,7 +774,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -896,7 +785,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -907,7 +796,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -918,7 +807,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -929,7 +818,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -940,7 +829,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -951,7 +840,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -962,7 +851,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -973,7 +862,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -984,7 +873,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -995,7 +884,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -1006,7 +895,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -1017,7 +906,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -1028,111 +917,12 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3">
-      <x:c r="A37" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="A38" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3">
-      <x:c r="A39" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>GSDDE</x:t>
+    <x:t>TNZTP</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,9 +35,6 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
@@ -47,91 +44,43 @@
     <x:t>ANHYT</x:t>
   </x:si>
   <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>AVPGY</x:t>
   </x:si>
   <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
+    <x:t>BMSTL</x:t>
   </x:si>
   <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
   </x:si>
   <x:si>
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
     <x:t>EUKYO</x:t>
   </x:si>
   <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
     <x:t>ISDMR</x:t>
   </x:si>
   <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
     <x:t>SKYMD</x:t>
   </x:si>
   <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
   </x:si>
   <x:si>
     <x:t>TRHOL</x:t>
@@ -527,7 +476,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C36"/>
+  <x:dimension ref="A1:C19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -736,193 +685,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:3">
-      <x:c r="A20" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3">
-      <x:c r="A21" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3">
-      <x:c r="A28" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:3">
-      <x:c r="A29" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:3">
-      <x:c r="A30" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:3">
-      <x:c r="A31" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3">
-      <x:c r="A32" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:3">
-      <x:c r="A33" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:3">
-      <x:c r="A34" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:3">
-      <x:c r="A35" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:3">
-      <x:c r="A36" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>TNZTP</x:t>
+    <x:t>BMSTL</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,58 +35,16 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANHYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
     <x:t>EFOR</x:t>
   </x:si>
   <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
     <x:t>EUKYO</x:t>
   </x:si>
   <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -437,7 +395,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -449,17 +407,6 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -476,7 +423,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C19"/>
+  <x:dimension ref="A1:C6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -492,7 +439,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -503,7 +450,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -514,7 +461,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -525,7 +472,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -536,155 +483,12 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:3">
-      <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:3">
-      <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:3">
-      <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:3">
-      <x:c r="A11" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:3">
-      <x:c r="A12" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:3">
-      <x:c r="A13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:3">
-      <x:c r="A14" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:3">
-      <x:c r="A15" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:3">
-      <x:c r="A16" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:3">
-      <x:c r="A17" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:3">
-      <x:c r="A18" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:3">
-      <x:c r="A19" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,25 +26,49 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>BMSTL</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -395,7 +419,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C1"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -407,6 +431,17 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -423,7 +458,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C6"/>
+  <x:dimension ref="A1:C13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -439,7 +474,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -450,7 +485,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -461,7 +496,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -472,7 +507,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -483,12 +518,89 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:3">
+      <x:c r="A7" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:3">
+      <x:c r="A8" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:3">
+      <x:c r="A9" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3">
+      <x:c r="A11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:3">
+      <x:c r="A12" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,46 +26,37 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
     <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANHYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
   </x:si>
   <x:si>
     <x:t>TUPRS</x:t>
@@ -419,7 +410,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -431,17 +422,6 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -458,7 +438,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C13"/>
+  <x:dimension ref="A1:C11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -474,7 +454,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -485,7 +465,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -496,7 +476,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -507,7 +487,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -518,7 +498,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -529,7 +509,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -540,7 +520,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -551,7 +531,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -562,7 +542,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -573,34 +553,12 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:3">
-      <x:c r="A12" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:3">
-      <x:c r="A13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,34 +26,31 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
     <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
     <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
@@ -410,7 +407,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C1"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -422,6 +419,17 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -438,7 +446,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C11"/>
+  <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -454,7 +462,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -465,7 +473,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -476,7 +484,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -487,7 +495,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -498,7 +506,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -509,7 +517,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -520,7 +528,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -531,34 +539,12 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:3">
-      <x:c r="A11" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,19 +26,31 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>BAHKM</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
   </x:si>
   <x:si>
     <x:t>ISDMR</x:t>
@@ -47,16 +59,13 @@
     <x:t>KCHOL</x:t>
   </x:si>
   <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
     <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
     <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -407,7 +416,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -429,6 +438,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -446,7 +466,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C9"/>
+  <x:dimension ref="A1:C11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -462,7 +482,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -473,7 +493,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -484,7 +504,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -495,7 +515,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -506,7 +526,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -517,7 +537,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -528,7 +548,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -539,12 +559,34 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3">
+      <x:c r="A11" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,46 +26,1894 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1YEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKMGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASUZU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BETAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
     <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIMSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERBOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
   </x:si>
   <x:si>
     <x:t>HUNER</x:t>
   </x:si>
   <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
   </x:si>
   <x:si>
     <x:t>ISDMR</x:t>
   </x:si>
   <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISVEA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARCL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
     <x:t>KCHOL</x:t>
   </x:si>
   <x:si>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KPEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
     <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
-    <x:t>RYGYO</x:t>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASFN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORZAX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUAGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUICK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAYSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUZYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAFKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SERNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SODSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOHOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SONME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRVGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SSAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAVHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TBORG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKNKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSPOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTRAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUREX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURGG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UCAYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UMPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VESBE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VESTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VEYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKFYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VSNMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAYLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YBTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YESIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKSLN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YONGA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YYAPI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YYLGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZEDUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZERGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZOREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZRGYO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -416,7 +2264,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C3"/>
+  <x:dimension ref="A1:C5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -449,6 +2297,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:3">
+      <x:c r="A5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -466,7 +2336,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C11"/>
+  <x:dimension ref="A1:C625"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -482,7 +2352,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -493,7 +2363,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -504,7 +2374,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -515,7 +2385,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -526,7 +2396,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -537,7 +2407,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -548,7 +2418,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -559,7 +2429,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -570,7 +2440,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -581,12 +2451,6766 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:3">
+      <x:c r="A12" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:3">
+      <x:c r="A49" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:3">
+      <x:c r="A50" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:3">
+      <x:c r="A51" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:3">
+      <x:c r="A52" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:3">
+      <x:c r="A53" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:3">
+      <x:c r="A54" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:3">
+      <x:c r="A55" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:3">
+      <x:c r="A56" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:3">
+      <x:c r="A57" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:3">
+      <x:c r="A58" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:3">
+      <x:c r="A59" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:3">
+      <x:c r="A60" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:3">
+      <x:c r="A61" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:3">
+      <x:c r="A62" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:3">
+      <x:c r="A63" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:3">
+      <x:c r="A64" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:3">
+      <x:c r="A65" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:3">
+      <x:c r="A66" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:3">
+      <x:c r="A67" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:3">
+      <x:c r="A68" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:3">
+      <x:c r="A69" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:3">
+      <x:c r="A70" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:3">
+      <x:c r="A71" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:3">
+      <x:c r="A72" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:3">
+      <x:c r="A73" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:3">
+      <x:c r="A74" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:3">
+      <x:c r="A75" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:3">
+      <x:c r="A76" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:3">
+      <x:c r="A77" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:3">
+      <x:c r="A78" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:3">
+      <x:c r="A79" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:3">
+      <x:c r="A80" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:3">
+      <x:c r="A81" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:3">
+      <x:c r="A82" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:3">
+      <x:c r="A83" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:3">
+      <x:c r="A84" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:3">
+      <x:c r="A85" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:3">
+      <x:c r="A86" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:3">
+      <x:c r="A87" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:3">
+      <x:c r="A88" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:3">
+      <x:c r="A89" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:3">
+      <x:c r="A90" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:3">
+      <x:c r="A91" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:3">
+      <x:c r="A92" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:3">
+      <x:c r="A93" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:3">
+      <x:c r="A94" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:3">
+      <x:c r="A95" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:3">
+      <x:c r="A96" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:3">
+      <x:c r="A97" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:3">
+      <x:c r="A98" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:3">
+      <x:c r="A99" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:3">
+      <x:c r="A100" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:3">
+      <x:c r="A101" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:3">
+      <x:c r="A102" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:3">
+      <x:c r="A103" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:3">
+      <x:c r="A104" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C104" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:3">
+      <x:c r="A105" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:3">
+      <x:c r="A106" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:3">
+      <x:c r="A107" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:3">
+      <x:c r="A108" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:3">
+      <x:c r="A109" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:3">
+      <x:c r="A110" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:3">
+      <x:c r="A111" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:3">
+      <x:c r="A112" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:3">
+      <x:c r="A113" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:3">
+      <x:c r="A114" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C114" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:3">
+      <x:c r="A115" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:3">
+      <x:c r="A116" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:3">
+      <x:c r="A117" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:3">
+      <x:c r="A118" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:3">
+      <x:c r="A119" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:3">
+      <x:c r="A120" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:3">
+      <x:c r="A121" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:3">
+      <x:c r="A122" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:3">
+      <x:c r="A123" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:3">
+      <x:c r="A124" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:3">
+      <x:c r="A125" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:3">
+      <x:c r="A126" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:3">
+      <x:c r="A127" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:3">
+      <x:c r="A128" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:3">
+      <x:c r="A129" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:3">
+      <x:c r="A130" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:3">
+      <x:c r="A131" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:3">
+      <x:c r="A132" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:3">
+      <x:c r="A133" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:3">
+      <x:c r="A134" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:3">
+      <x:c r="A135" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:3">
+      <x:c r="A136" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:3">
+      <x:c r="A137" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:3">
+      <x:c r="A138" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:3">
+      <x:c r="A139" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:3">
+      <x:c r="A140" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:3">
+      <x:c r="A141" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:3">
+      <x:c r="A142" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:3">
+      <x:c r="A143" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:3">
+      <x:c r="A144" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:3">
+      <x:c r="A145" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:3">
+      <x:c r="A146" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:3">
+      <x:c r="A147" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:3">
+      <x:c r="A148" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:3">
+      <x:c r="A149" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:3">
+      <x:c r="A150" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:3">
+      <x:c r="A151" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:3">
+      <x:c r="A152" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:3">
+      <x:c r="A153" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:3">
+      <x:c r="A154" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:3">
+      <x:c r="A155" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:3">
+      <x:c r="A156" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:3">
+      <x:c r="A157" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:3">
+      <x:c r="A158" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:3">
+      <x:c r="A159" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:3">
+      <x:c r="A160" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:3">
+      <x:c r="A161" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:3">
+      <x:c r="A162" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:3">
+      <x:c r="A163" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:3">
+      <x:c r="A164" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:3">
+      <x:c r="A165" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:3">
+      <x:c r="A166" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:3">
+      <x:c r="A167" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:3">
+      <x:c r="A168" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:3">
+      <x:c r="A169" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:3">
+      <x:c r="A170" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:3">
+      <x:c r="A171" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:3">
+      <x:c r="A172" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:3">
+      <x:c r="A173" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:3">
+      <x:c r="A174" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C174" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:3">
+      <x:c r="A175" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C175" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:3">
+      <x:c r="A176" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C176" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:3">
+      <x:c r="A177" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C177" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:3">
+      <x:c r="A178" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C178" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:3">
+      <x:c r="A179" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C179" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:3">
+      <x:c r="A180" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B180" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C180" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:3">
+      <x:c r="A181" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="B181" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C181" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:3">
+      <x:c r="A182" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C182" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:3">
+      <x:c r="A183" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C183" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:3">
+      <x:c r="A184" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C184" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:3">
+      <x:c r="A185" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C185" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:3">
+      <x:c r="A186" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C186" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:3">
+      <x:c r="A187" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C187" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:3">
+      <x:c r="A188" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B188" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C188" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:3">
+      <x:c r="A189" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C189" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:3">
+      <x:c r="A190" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C190" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:3">
+      <x:c r="A191" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C191" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:3">
+      <x:c r="A192" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C192" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:3">
+      <x:c r="A193" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C193" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:3">
+      <x:c r="A194" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C194" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:3">
+      <x:c r="A195" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C195" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:3">
+      <x:c r="A196" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C196" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:3">
+      <x:c r="A197" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B197" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C197" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:3">
+      <x:c r="A198" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B198" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C198" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:3">
+      <x:c r="A199" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B199" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C199" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:3">
+      <x:c r="A200" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B200" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C200" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:3">
+      <x:c r="A201" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B201" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C201" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:3">
+      <x:c r="A202" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B202" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C202" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" spans="1:3">
+      <x:c r="A203" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B203" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C203" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:3">
+      <x:c r="A204" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B204" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C204" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:3">
+      <x:c r="A205" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B205" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C205" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:3">
+      <x:c r="A206" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B206" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C206" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" spans="1:3">
+      <x:c r="A207" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B207" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C207" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:3">
+      <x:c r="A208" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B208" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C208" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:3">
+      <x:c r="A209" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B209" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C209" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" spans="1:3">
+      <x:c r="A210" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B210" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C210" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" spans="1:3">
+      <x:c r="A211" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B211" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C211" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:3">
+      <x:c r="A212" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B212" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C212" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" spans="1:3">
+      <x:c r="A213" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B213" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C213" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:3">
+      <x:c r="A214" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="B214" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C214" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:3">
+      <x:c r="A215" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B215" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C215" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" spans="1:3">
+      <x:c r="A216" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B216" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C216" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:3">
+      <x:c r="A217" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="B217" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C217" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" spans="1:3">
+      <x:c r="A218" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="B218" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C218" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" spans="1:3">
+      <x:c r="A219" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B219" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C219" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" spans="1:3">
+      <x:c r="A220" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B220" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C220" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" spans="1:3">
+      <x:c r="A221" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="B221" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C221" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" spans="1:3">
+      <x:c r="A222" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B222" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C222" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" spans="1:3">
+      <x:c r="A223" s="0" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B223" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C223" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" spans="1:3">
+      <x:c r="A224" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B224" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C224" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" spans="1:3">
+      <x:c r="A225" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B225" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C225" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" spans="1:3">
+      <x:c r="A226" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B226" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C226" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" spans="1:3">
+      <x:c r="A227" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="B227" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C227" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" spans="1:3">
+      <x:c r="A228" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B228" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C228" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" spans="1:3">
+      <x:c r="A229" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="B229" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C229" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" spans="1:3">
+      <x:c r="A230" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B230" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C230" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" spans="1:3">
+      <x:c r="A231" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B231" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C231" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" spans="1:3">
+      <x:c r="A232" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="B232" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C232" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" spans="1:3">
+      <x:c r="A233" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="B233" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C233" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" spans="1:3">
+      <x:c r="A234" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B234" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C234" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" spans="1:3">
+      <x:c r="A235" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="B235" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C235" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" spans="1:3">
+      <x:c r="A236" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B236" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C236" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" spans="1:3">
+      <x:c r="A237" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B237" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C237" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" spans="1:3">
+      <x:c r="A238" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="B238" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C238" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" spans="1:3">
+      <x:c r="A239" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="B239" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C239" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" spans="1:3">
+      <x:c r="A240" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B240" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C240" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" spans="1:3">
+      <x:c r="A241" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="B241" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C241" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" spans="1:3">
+      <x:c r="A242" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B242" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C242" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" spans="1:3">
+      <x:c r="A243" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="B243" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C243" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" spans="1:3">
+      <x:c r="A244" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B244" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C244" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" spans="1:3">
+      <x:c r="A245" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="B245" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C245" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" spans="1:3">
+      <x:c r="A246" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B246" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C246" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" spans="1:3">
+      <x:c r="A247" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="B247" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C247" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" spans="1:3">
+      <x:c r="A248" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B248" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C248" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" spans="1:3">
+      <x:c r="A249" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="B249" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C249" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" spans="1:3">
+      <x:c r="A250" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B250" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C250" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" spans="1:3">
+      <x:c r="A251" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="B251" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C251" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" spans="1:3">
+      <x:c r="A252" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B252" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C252" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" spans="1:3">
+      <x:c r="A253" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="B253" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C253" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" spans="1:3">
+      <x:c r="A254" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B254" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C254" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" spans="1:3">
+      <x:c r="A255" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B255" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C255" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" spans="1:3">
+      <x:c r="A256" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="B256" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C256" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" spans="1:3">
+      <x:c r="A257" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B257" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C257" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" spans="1:3">
+      <x:c r="A258" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B258" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C258" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" spans="1:3">
+      <x:c r="A259" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B259" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C259" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" spans="1:3">
+      <x:c r="A260" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="B260" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C260" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" spans="1:3">
+      <x:c r="A261" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="B261" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C261" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" spans="1:3">
+      <x:c r="A262" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="B262" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C262" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" spans="1:3">
+      <x:c r="A263" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B263" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C263" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" spans="1:3">
+      <x:c r="A264" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="B264" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C264" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" spans="1:3">
+      <x:c r="A265" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="B265" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C265" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" spans="1:3">
+      <x:c r="A266" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="B266" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C266" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" spans="1:3">
+      <x:c r="A267" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="B267" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C267" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" spans="1:3">
+      <x:c r="A268" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="B268" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C268" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" spans="1:3">
+      <x:c r="A269" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="B269" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C269" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" spans="1:3">
+      <x:c r="A270" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="B270" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C270" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" spans="1:3">
+      <x:c r="A271" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="B271" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C271" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" spans="1:3">
+      <x:c r="A272" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B272" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C272" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" spans="1:3">
+      <x:c r="A273" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="B273" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C273" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" spans="1:3">
+      <x:c r="A274" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="B274" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C274" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" spans="1:3">
+      <x:c r="A275" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B275" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C275" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" spans="1:3">
+      <x:c r="A276" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B276" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C276" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" spans="1:3">
+      <x:c r="A277" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="B277" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C277" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" spans="1:3">
+      <x:c r="A278" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B278" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C278" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" spans="1:3">
+      <x:c r="A279" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B279" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C279" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" spans="1:3">
+      <x:c r="A280" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B280" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C280" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" spans="1:3">
+      <x:c r="A281" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B281" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C281" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" spans="1:3">
+      <x:c r="A282" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B282" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C282" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" spans="1:3">
+      <x:c r="A283" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="B283" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C283" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" spans="1:3">
+      <x:c r="A284" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B284" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C284" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" spans="1:3">
+      <x:c r="A285" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="B285" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C285" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" spans="1:3">
+      <x:c r="A286" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B286" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C286" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" spans="1:3">
+      <x:c r="A287" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B287" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C287" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" spans="1:3">
+      <x:c r="A288" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="B288" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C288" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" spans="1:3">
+      <x:c r="A289" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="B289" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C289" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" spans="1:3">
+      <x:c r="A290" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B290" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C290" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" spans="1:3">
+      <x:c r="A291" s="0" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="B291" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C291" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" spans="1:3">
+      <x:c r="A292" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="B292" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C292" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" spans="1:3">
+      <x:c r="A293" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B293" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C293" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" spans="1:3">
+      <x:c r="A294" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B294" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C294" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" spans="1:3">
+      <x:c r="A295" s="0" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="B295" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C295" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" spans="1:3">
+      <x:c r="A296" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B296" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C296" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" spans="1:3">
+      <x:c r="A297" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="B297" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C297" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" spans="1:3">
+      <x:c r="A298" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B298" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C298" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" spans="1:3">
+      <x:c r="A299" s="0" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B299" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C299" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" spans="1:3">
+      <x:c r="A300" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B300" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C300" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" spans="1:3">
+      <x:c r="A301" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="B301" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C301" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" spans="1:3">
+      <x:c r="A302" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B302" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C302" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" spans="1:3">
+      <x:c r="A303" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="B303" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C303" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" spans="1:3">
+      <x:c r="A304" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B304" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C304" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" spans="1:3">
+      <x:c r="A305" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B305" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C305" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" spans="1:3">
+      <x:c r="A306" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B306" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C306" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" spans="1:3">
+      <x:c r="A307" s="0" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="B307" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C307" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" spans="1:3">
+      <x:c r="A308" s="0" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B308" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C308" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" spans="1:3">
+      <x:c r="A309" s="0" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="B309" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C309" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" spans="1:3">
+      <x:c r="A310" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B310" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C310" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" spans="1:3">
+      <x:c r="A311" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B311" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C311" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" spans="1:3">
+      <x:c r="A312" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="B312" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C312" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" spans="1:3">
+      <x:c r="A313" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B313" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C313" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" spans="1:3">
+      <x:c r="A314" s="0" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B314" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C314" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" spans="1:3">
+      <x:c r="A315" s="0" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B315" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C315" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" spans="1:3">
+      <x:c r="A316" s="0" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B316" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C316" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" spans="1:3">
+      <x:c r="A317" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B317" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C317" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" spans="1:3">
+      <x:c r="A318" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B318" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C318" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" spans="1:3">
+      <x:c r="A319" s="0" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="B319" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C319" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" spans="1:3">
+      <x:c r="A320" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B320" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C320" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" spans="1:3">
+      <x:c r="A321" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B321" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C321" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" spans="1:3">
+      <x:c r="A322" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="B322" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C322" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" spans="1:3">
+      <x:c r="A323" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B323" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C323" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" spans="1:3">
+      <x:c r="A324" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B324" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C324" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" spans="1:3">
+      <x:c r="A325" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B325" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C325" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" spans="1:3">
+      <x:c r="A326" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B326" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C326" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" spans="1:3">
+      <x:c r="A327" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B327" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C327" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" spans="1:3">
+      <x:c r="A328" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="B328" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C328" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" spans="1:3">
+      <x:c r="A329" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B329" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C329" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" spans="1:3">
+      <x:c r="A330" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B330" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C330" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" spans="1:3">
+      <x:c r="A331" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="B331" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C331" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" spans="1:3">
+      <x:c r="A332" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B332" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C332" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" spans="1:3">
+      <x:c r="A333" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="B333" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C333" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" spans="1:3">
+      <x:c r="A334" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B334" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C334" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" spans="1:3">
+      <x:c r="A335" s="0" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="B335" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C335" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" spans="1:3">
+      <x:c r="A336" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B336" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C336" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" spans="1:3">
+      <x:c r="A337" s="0" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B337" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C337" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338" spans="1:3">
+      <x:c r="A338" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B338" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C338" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" spans="1:3">
+      <x:c r="A339" s="0" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B339" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C339" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" spans="1:3">
+      <x:c r="A340" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="B340" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C340" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341" spans="1:3">
+      <x:c r="A341" s="0" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="B341" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C341" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" spans="1:3">
+      <x:c r="A342" s="0" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="B342" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C342" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" spans="1:3">
+      <x:c r="A343" s="0" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="B343" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C343" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" spans="1:3">
+      <x:c r="A344" s="0" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="B344" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C344" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" spans="1:3">
+      <x:c r="A345" s="0" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B345" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C345" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" spans="1:3">
+      <x:c r="A346" s="0" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="B346" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C346" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" spans="1:3">
+      <x:c r="A347" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="B347" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C347" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" spans="1:3">
+      <x:c r="A348" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="B348" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C348" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" spans="1:3">
+      <x:c r="A349" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="B349" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C349" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" spans="1:3">
+      <x:c r="A350" s="0" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="B350" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C350" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" spans="1:3">
+      <x:c r="A351" s="0" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="B351" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C351" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" spans="1:3">
+      <x:c r="A352" s="0" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="B352" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C352" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" spans="1:3">
+      <x:c r="A353" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="B353" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C353" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" spans="1:3">
+      <x:c r="A354" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="B354" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C354" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" spans="1:3">
+      <x:c r="A355" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="B355" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C355" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" spans="1:3">
+      <x:c r="A356" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="B356" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C356" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" spans="1:3">
+      <x:c r="A357" s="0" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="B357" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C357" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" spans="1:3">
+      <x:c r="A358" s="0" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="B358" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C358" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" spans="1:3">
+      <x:c r="A359" s="0" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="B359" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C359" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" spans="1:3">
+      <x:c r="A360" s="0" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="B360" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C360" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" spans="1:3">
+      <x:c r="A361" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="B361" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C361" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" spans="1:3">
+      <x:c r="A362" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="B362" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C362" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" spans="1:3">
+      <x:c r="A363" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B363" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C363" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364" spans="1:3">
+      <x:c r="A364" s="0" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="B364" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C364" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365" spans="1:3">
+      <x:c r="A365" s="0" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="B365" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C365" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366" spans="1:3">
+      <x:c r="A366" s="0" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="B366" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C366" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367" spans="1:3">
+      <x:c r="A367" s="0" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="B367" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C367" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368" spans="1:3">
+      <x:c r="A368" s="0" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="B368" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C368" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369" spans="1:3">
+      <x:c r="A369" s="0" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="B369" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C369" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370" spans="1:3">
+      <x:c r="A370" s="0" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="B370" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C370" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" spans="1:3">
+      <x:c r="A371" s="0" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="B371" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C371" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" spans="1:3">
+      <x:c r="A372" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="B372" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C372" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" spans="1:3">
+      <x:c r="A373" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="B373" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C373" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" spans="1:3">
+      <x:c r="A374" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="B374" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C374" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" spans="1:3">
+      <x:c r="A375" s="0" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="B375" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C375" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" spans="1:3">
+      <x:c r="A376" s="0" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="B376" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C376" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" spans="1:3">
+      <x:c r="A377" s="0" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="B377" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C377" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" spans="1:3">
+      <x:c r="A378" s="0" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="B378" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C378" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" spans="1:3">
+      <x:c r="A379" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B379" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C379" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" spans="1:3">
+      <x:c r="A380" s="0" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="B380" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C380" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" spans="1:3">
+      <x:c r="A381" s="0" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B381" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C381" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" spans="1:3">
+      <x:c r="A382" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="B382" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C382" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" spans="1:3">
+      <x:c r="A383" s="0" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="B383" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C383" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" spans="1:3">
+      <x:c r="A384" s="0" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B384" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C384" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" spans="1:3">
+      <x:c r="A385" s="0" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="B385" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C385" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" spans="1:3">
+      <x:c r="A386" s="0" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="B386" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C386" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" spans="1:3">
+      <x:c r="A387" s="0" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="B387" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C387" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" spans="1:3">
+      <x:c r="A388" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="B388" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C388" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" spans="1:3">
+      <x:c r="A389" s="0" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="B389" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C389" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" spans="1:3">
+      <x:c r="A390" s="0" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="B390" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C390" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" spans="1:3">
+      <x:c r="A391" s="0" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="B391" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C391" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" spans="1:3">
+      <x:c r="A392" s="0" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="B392" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C392" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" spans="1:3">
+      <x:c r="A393" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="B393" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C393" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" spans="1:3">
+      <x:c r="A394" s="0" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B394" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C394" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" spans="1:3">
+      <x:c r="A395" s="0" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="B395" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C395" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" spans="1:3">
+      <x:c r="A396" s="0" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="B396" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C396" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" spans="1:3">
+      <x:c r="A397" s="0" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="B397" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C397" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" spans="1:3">
+      <x:c r="A398" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="B398" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C398" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" spans="1:3">
+      <x:c r="A399" s="0" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B399" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C399" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" spans="1:3">
+      <x:c r="A400" s="0" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="B400" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C400" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" spans="1:3">
+      <x:c r="A401" s="0" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B401" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C401" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" spans="1:3">
+      <x:c r="A402" s="0" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="B402" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C402" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" spans="1:3">
+      <x:c r="A403" s="0" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B403" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C403" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" spans="1:3">
+      <x:c r="A404" s="0" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="B404" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C404" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" spans="1:3">
+      <x:c r="A405" s="0" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="B405" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C405" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" spans="1:3">
+      <x:c r="A406" s="0" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B406" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C406" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" spans="1:3">
+      <x:c r="A407" s="0" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="B407" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C407" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" spans="1:3">
+      <x:c r="A408" s="0" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="B408" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C408" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" spans="1:3">
+      <x:c r="A409" s="0" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="B409" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C409" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" spans="1:3">
+      <x:c r="A410" s="0" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="B410" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C410" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" spans="1:3">
+      <x:c r="A411" s="0" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="B411" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C411" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" spans="1:3">
+      <x:c r="A412" s="0" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="B412" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C412" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" spans="1:3">
+      <x:c r="A413" s="0" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="B413" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C413" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" spans="1:3">
+      <x:c r="A414" s="0" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="B414" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C414" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" spans="1:3">
+      <x:c r="A415" s="0" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="B415" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C415" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" spans="1:3">
+      <x:c r="A416" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="B416" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C416" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" spans="1:3">
+      <x:c r="A417" s="0" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="B417" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C417" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" spans="1:3">
+      <x:c r="A418" s="0" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="B418" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C418" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" spans="1:3">
+      <x:c r="A419" s="0" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B419" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C419" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" spans="1:3">
+      <x:c r="A420" s="0" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="B420" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C420" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" spans="1:3">
+      <x:c r="A421" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="B421" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C421" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" spans="1:3">
+      <x:c r="A422" s="0" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="B422" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C422" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" spans="1:3">
+      <x:c r="A423" s="0" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="B423" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C423" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" spans="1:3">
+      <x:c r="A424" s="0" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="B424" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C424" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" spans="1:3">
+      <x:c r="A425" s="0" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="B425" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C425" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" spans="1:3">
+      <x:c r="A426" s="0" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B426" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C426" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" spans="1:3">
+      <x:c r="A427" s="0" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="B427" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C427" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" spans="1:3">
+      <x:c r="A428" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="B428" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C428" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" spans="1:3">
+      <x:c r="A429" s="0" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B429" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C429" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" spans="1:3">
+      <x:c r="A430" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="B430" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C430" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" spans="1:3">
+      <x:c r="A431" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="B431" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C431" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" spans="1:3">
+      <x:c r="A432" s="0" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="B432" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C432" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" spans="1:3">
+      <x:c r="A433" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="B433" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C433" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" spans="1:3">
+      <x:c r="A434" s="0" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="B434" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C434" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" spans="1:3">
+      <x:c r="A435" s="0" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="B435" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C435" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" spans="1:3">
+      <x:c r="A436" s="0" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="B436" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C436" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" spans="1:3">
+      <x:c r="A437" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="B437" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C437" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" spans="1:3">
+      <x:c r="A438" s="0" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="B438" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C438" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" spans="1:3">
+      <x:c r="A439" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="B439" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C439" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" spans="1:3">
+      <x:c r="A440" s="0" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="B440" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C440" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" spans="1:3">
+      <x:c r="A441" s="0" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="B441" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C441" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" spans="1:3">
+      <x:c r="A442" s="0" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="B442" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C442" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443" spans="1:3">
+      <x:c r="A443" s="0" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="B443" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C443" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" spans="1:3">
+      <x:c r="A444" s="0" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="B444" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C444" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445" spans="1:3">
+      <x:c r="A445" s="0" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="B445" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C445" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" spans="1:3">
+      <x:c r="A446" s="0" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B446" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C446" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447" spans="1:3">
+      <x:c r="A447" s="0" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B447" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C447" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448" spans="1:3">
+      <x:c r="A448" s="0" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B448" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C448" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449" spans="1:3">
+      <x:c r="A449" s="0" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B449" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C449" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450" spans="1:3">
+      <x:c r="A450" s="0" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="B450" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C450" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451" spans="1:3">
+      <x:c r="A451" s="0" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="B451" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C451" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452" spans="1:3">
+      <x:c r="A452" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B452" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C452" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453" spans="1:3">
+      <x:c r="A453" s="0" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="B453" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C453" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454" spans="1:3">
+      <x:c r="A454" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B454" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C454" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455" spans="1:3">
+      <x:c r="A455" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B455" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C455" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456" spans="1:3">
+      <x:c r="A456" s="0" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="B456" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C456" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457" spans="1:3">
+      <x:c r="A457" s="0" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="B457" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C457" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458" spans="1:3">
+      <x:c r="A458" s="0" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B458" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C458" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459" spans="1:3">
+      <x:c r="A459" s="0" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="B459" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C459" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460" spans="1:3">
+      <x:c r="A460" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="B460" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C460" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461" spans="1:3">
+      <x:c r="A461" s="0" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B461" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C461" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462" spans="1:3">
+      <x:c r="A462" s="0" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="B462" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C462" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463" spans="1:3">
+      <x:c r="A463" s="0" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="B463" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C463" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464" spans="1:3">
+      <x:c r="A464" s="0" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="B464" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C464" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465" spans="1:3">
+      <x:c r="A465" s="0" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="B465" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C465" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466" spans="1:3">
+      <x:c r="A466" s="0" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="B466" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C466" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467" spans="1:3">
+      <x:c r="A467" s="0" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="B467" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C467" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468" spans="1:3">
+      <x:c r="A468" s="0" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B468" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C468" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469" spans="1:3">
+      <x:c r="A469" s="0" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="B469" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C469" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470" spans="1:3">
+      <x:c r="A470" s="0" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="B470" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C470" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471" spans="1:3">
+      <x:c r="A471" s="0" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="B471" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C471" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472" spans="1:3">
+      <x:c r="A472" s="0" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="B472" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C472" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473" spans="1:3">
+      <x:c r="A473" s="0" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B473" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C473" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474" spans="1:3">
+      <x:c r="A474" s="0" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B474" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C474" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475" spans="1:3">
+      <x:c r="A475" s="0" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="B475" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C475" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476" spans="1:3">
+      <x:c r="A476" s="0" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="B476" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C476" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477" spans="1:3">
+      <x:c r="A477" s="0" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B477" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C477" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478" spans="1:3">
+      <x:c r="A478" s="0" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="B478" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C478" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479" spans="1:3">
+      <x:c r="A479" s="0" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="B479" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C479" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480" spans="1:3">
+      <x:c r="A480" s="0" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B480" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C480" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481" spans="1:3">
+      <x:c r="A481" s="0" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="B481" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C481" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482" spans="1:3">
+      <x:c r="A482" s="0" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="B482" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C482" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483" spans="1:3">
+      <x:c r="A483" s="0" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B483" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C483" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484" spans="1:3">
+      <x:c r="A484" s="0" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="B484" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C484" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485" spans="1:3">
+      <x:c r="A485" s="0" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="B485" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C485" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486" spans="1:3">
+      <x:c r="A486" s="0" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B486" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C486" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487" spans="1:3">
+      <x:c r="A487" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="B487" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C487" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488" spans="1:3">
+      <x:c r="A488" s="0" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="B488" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C488" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489" spans="1:3">
+      <x:c r="A489" s="0" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B489" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C489" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490" spans="1:3">
+      <x:c r="A490" s="0" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="B490" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C490" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491" spans="1:3">
+      <x:c r="A491" s="0" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="B491" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C491" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492" spans="1:3">
+      <x:c r="A492" s="0" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="B492" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C492" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493" spans="1:3">
+      <x:c r="A493" s="0" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="B493" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C493" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494" spans="1:3">
+      <x:c r="A494" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="B494" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C494" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495" spans="1:3">
+      <x:c r="A495" s="0" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="B495" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C495" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" spans="1:3">
+      <x:c r="A496" s="0" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="B496" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C496" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497" spans="1:3">
+      <x:c r="A497" s="0" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="B497" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C497" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498" spans="1:3">
+      <x:c r="A498" s="0" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="B498" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C498" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499" spans="1:3">
+      <x:c r="A499" s="0" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="B499" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C499" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" spans="1:3">
+      <x:c r="A500" s="0" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="B500" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C500" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501" spans="1:3">
+      <x:c r="A501" s="0" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="B501" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C501" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" spans="1:3">
+      <x:c r="A502" s="0" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="B502" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C502" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503" spans="1:3">
+      <x:c r="A503" s="0" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="B503" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C503" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504" spans="1:3">
+      <x:c r="A504" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="B504" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C504" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505" spans="1:3">
+      <x:c r="A505" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="B505" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C505" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506" spans="1:3">
+      <x:c r="A506" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="B506" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C506" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507" spans="1:3">
+      <x:c r="A507" s="0" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="B507" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C507" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" spans="1:3">
+      <x:c r="A508" s="0" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="B508" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C508" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509" spans="1:3">
+      <x:c r="A509" s="0" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="B509" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C509" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510" spans="1:3">
+      <x:c r="A510" s="0" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="B510" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C510" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511" spans="1:3">
+      <x:c r="A511" s="0" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="B511" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C511" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512" spans="1:3">
+      <x:c r="A512" s="0" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B512" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C512" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513" spans="1:3">
+      <x:c r="A513" s="0" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="B513" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C513" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514" spans="1:3">
+      <x:c r="A514" s="0" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="B514" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C514" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515" spans="1:3">
+      <x:c r="A515" s="0" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="B515" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C515" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516" spans="1:3">
+      <x:c r="A516" s="0" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="B516" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C516" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517" spans="1:3">
+      <x:c r="A517" s="0" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="B517" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C517" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518" spans="1:3">
+      <x:c r="A518" s="0" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="B518" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C518" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519" spans="1:3">
+      <x:c r="A519" s="0" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="B519" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C519" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520" spans="1:3">
+      <x:c r="A520" s="0" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="B520" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C520" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521" spans="1:3">
+      <x:c r="A521" s="0" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="B521" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C521" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522" spans="1:3">
+      <x:c r="A522" s="0" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="B522" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C522" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523" spans="1:3">
+      <x:c r="A523" s="0" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="B523" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C523" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524" spans="1:3">
+      <x:c r="A524" s="0" t="s">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="B524" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C524" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525" spans="1:3">
+      <x:c r="A525" s="0" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="B525" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C525" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526" spans="1:3">
+      <x:c r="A526" s="0" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="B526" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C526" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527" spans="1:3">
+      <x:c r="A527" s="0" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="B527" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C527" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528" spans="1:3">
+      <x:c r="A528" s="0" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="B528" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C528" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529" spans="1:3">
+      <x:c r="A529" s="0" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B529" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C529" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530" spans="1:3">
+      <x:c r="A530" s="0" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="B530" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C530" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531" spans="1:3">
+      <x:c r="A531" s="0" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="B531" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C531" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532" spans="1:3">
+      <x:c r="A532" s="0" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="B532" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C532" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533" spans="1:3">
+      <x:c r="A533" s="0" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="B533" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C533" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534" spans="1:3">
+      <x:c r="A534" s="0" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="B534" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C534" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535" spans="1:3">
+      <x:c r="A535" s="0" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B535" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C535" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536" spans="1:3">
+      <x:c r="A536" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="B536" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C536" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537" spans="1:3">
+      <x:c r="A537" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="B537" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C537" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538" spans="1:3">
+      <x:c r="A538" s="0" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="B538" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C538" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539" spans="1:3">
+      <x:c r="A539" s="0" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="B539" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C539" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540" spans="1:3">
+      <x:c r="A540" s="0" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="B540" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C540" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541" spans="1:3">
+      <x:c r="A541" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="B541" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C541" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542" spans="1:3">
+      <x:c r="A542" s="0" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="B542" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C542" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543" spans="1:3">
+      <x:c r="A543" s="0" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="B543" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C543" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544" spans="1:3">
+      <x:c r="A544" s="0" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="B544" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C544" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545" spans="1:3">
+      <x:c r="A545" s="0" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="B545" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C545" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546" spans="1:3">
+      <x:c r="A546" s="0" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="B546" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C546" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547" spans="1:3">
+      <x:c r="A547" s="0" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="B547" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C547" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548" spans="1:3">
+      <x:c r="A548" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="B548" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C548" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549" spans="1:3">
+      <x:c r="A549" s="0" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="B549" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C549" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550" spans="1:3">
+      <x:c r="A550" s="0" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="B550" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C550" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551" spans="1:3">
+      <x:c r="A551" s="0" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="B551" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C551" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552" spans="1:3">
+      <x:c r="A552" s="0" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="B552" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C552" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553" spans="1:3">
+      <x:c r="A553" s="0" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="B553" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C553" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554" spans="1:3">
+      <x:c r="A554" s="0" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="B554" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C554" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555" spans="1:3">
+      <x:c r="A555" s="0" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="B555" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C555" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556" spans="1:3">
+      <x:c r="A556" s="0" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="B556" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C556" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557" spans="1:3">
+      <x:c r="A557" s="0" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="B557" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C557" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558" spans="1:3">
+      <x:c r="A558" s="0" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="B558" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C558" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559" spans="1:3">
+      <x:c r="A559" s="0" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B559" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C559" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560" spans="1:3">
+      <x:c r="A560" s="0" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="B560" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C560" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561" spans="1:3">
+      <x:c r="A561" s="0" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="B561" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C561" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562" spans="1:3">
+      <x:c r="A562" s="0" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="B562" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C562" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563" spans="1:3">
+      <x:c r="A563" s="0" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="B563" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C563" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564" spans="1:3">
+      <x:c r="A564" s="0" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="B564" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C564" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565" spans="1:3">
+      <x:c r="A565" s="0" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="B565" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C565" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566" spans="1:3">
+      <x:c r="A566" s="0" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="B566" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C566" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567" spans="1:3">
+      <x:c r="A567" s="0" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="B567" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C567" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568" spans="1:3">
+      <x:c r="A568" s="0" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="B568" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C568" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569" spans="1:3">
+      <x:c r="A569" s="0" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="B569" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C569" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570" spans="1:3">
+      <x:c r="A570" s="0" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="B570" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C570" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571" spans="1:3">
+      <x:c r="A571" s="0" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="B571" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C571" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572" spans="1:3">
+      <x:c r="A572" s="0" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="B572" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C572" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573" spans="1:3">
+      <x:c r="A573" s="0" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="B573" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C573" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="574" spans="1:3">
+      <x:c r="A574" s="0" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="B574" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C574" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575" spans="1:3">
+      <x:c r="A575" s="0" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="B575" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C575" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="576" spans="1:3">
+      <x:c r="A576" s="0" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="B576" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C576" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="577" spans="1:3">
+      <x:c r="A577" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="B577" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C577" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="578" spans="1:3">
+      <x:c r="A578" s="0" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="B578" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C578" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579" spans="1:3">
+      <x:c r="A579" s="0" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="B579" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C579" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="580" spans="1:3">
+      <x:c r="A580" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="B580" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C580" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581" spans="1:3">
+      <x:c r="A581" s="0" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="B581" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C581" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582" spans="1:3">
+      <x:c r="A582" s="0" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="B582" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C582" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="583" spans="1:3">
+      <x:c r="A583" s="0" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="B583" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C583" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584" spans="1:3">
+      <x:c r="A584" s="0" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="B584" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C584" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="585" spans="1:3">
+      <x:c r="A585" s="0" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B585" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C585" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586" spans="1:3">
+      <x:c r="A586" s="0" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="B586" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C586" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587" spans="1:3">
+      <x:c r="A587" s="0" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="B587" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C587" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="588" spans="1:3">
+      <x:c r="A588" s="0" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="B588" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C588" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589" spans="1:3">
+      <x:c r="A589" s="0" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="B589" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C589" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="590" spans="1:3">
+      <x:c r="A590" s="0" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B590" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C590" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591" spans="1:3">
+      <x:c r="A591" s="0" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="B591" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C591" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="592" spans="1:3">
+      <x:c r="A592" s="0" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="B592" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C592" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593" spans="1:3">
+      <x:c r="A593" s="0" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="B593" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C593" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594" spans="1:3">
+      <x:c r="A594" s="0" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="B594" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C594" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="595" spans="1:3">
+      <x:c r="A595" s="0" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="B595" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C595" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596" spans="1:3">
+      <x:c r="A596" s="0" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="B596" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C596" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="597" spans="1:3">
+      <x:c r="A597" s="0" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="B597" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C597" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598" spans="1:3">
+      <x:c r="A598" s="0" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="B598" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C598" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="599" spans="1:3">
+      <x:c r="A599" s="0" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B599" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C599" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600" spans="1:3">
+      <x:c r="A600" s="0" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="B600" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C600" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601" spans="1:3">
+      <x:c r="A601" s="0" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="B601" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C601" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="602" spans="1:3">
+      <x:c r="A602" s="0" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="B602" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C602" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603" spans="1:3">
+      <x:c r="A603" s="0" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="B603" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C603" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604" spans="1:3">
+      <x:c r="A604" s="0" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="B604" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C604" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605" spans="1:3">
+      <x:c r="A605" s="0" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="B605" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C605" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606" spans="1:3">
+      <x:c r="A606" s="0" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="B606" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C606" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607" spans="1:3">
+      <x:c r="A607" s="0" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="B607" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C607" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608" spans="1:3">
+      <x:c r="A608" s="0" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B608" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C608" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609" spans="1:3">
+      <x:c r="A609" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="B609" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C609" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610" spans="1:3">
+      <x:c r="A610" s="0" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="B610" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C610" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611" spans="1:3">
+      <x:c r="A611" s="0" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="B611" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C611" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612" spans="1:3">
+      <x:c r="A612" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="B612" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C612" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613" spans="1:3">
+      <x:c r="A613" s="0" t="s">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="B613" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C613" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614" spans="1:3">
+      <x:c r="A614" s="0" t="s">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="B614" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C614" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615" spans="1:3">
+      <x:c r="A615" s="0" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="B615" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C615" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616" spans="1:3">
+      <x:c r="A616" s="0" t="s">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="B616" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C616" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617" spans="1:3">
+      <x:c r="A617" s="0" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="B617" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C617" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618" spans="1:3">
+      <x:c r="A618" s="0" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="B618" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C618" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619" spans="1:3">
+      <x:c r="A619" s="0" t="s">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="B619" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C619" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620" spans="1:3">
+      <x:c r="A620" s="0" t="s">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="B620" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C620" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621" spans="1:3">
+      <x:c r="A621" s="0" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="B621" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C621" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622" spans="1:3">
+      <x:c r="A622" s="0" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="B622" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C622" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623" spans="1:3">
+      <x:c r="A623" s="0" t="s">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="B623" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C623" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624" spans="1:3">
+      <x:c r="A624" s="0" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="B624" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C624" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625" spans="1:3">
+      <x:c r="A625" s="0" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="B625" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C625" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,34 +26,1504 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1YEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKMGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASUZU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BETAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIMSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERBOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISVEA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARCL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KPEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
   </x:si>
   <x:si>
     <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASFN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORZAX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUAGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUICK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAYSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUZYE</x:t>
   </x:si>
   <x:si>
     <x:t>RYGYO</x:t>
@@ -62,13 +1532,388 @@
     <x:t>RYSAS</x:t>
   </x:si>
   <x:si>
+    <x:t>SAFKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SERNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SODSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOHOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SONME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRVGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SSAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAVHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TBORG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
     <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
-    <x:t>TRMET</x:t>
+    <x:t>TKNKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSPOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTRAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUKAS</x:t>
   </x:si>
   <x:si>
     <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUREX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURGG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UCAYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UMPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VESBE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VESTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VEYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKFYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VSNMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAYLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YBTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YESIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKSLN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YONGA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YYAPI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YYLGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZEDUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZERGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZOREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZRGYO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -469,7 +2314,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C12"/>
+  <x:dimension ref="A1:C627"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -601,6 +2446,6771 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:3">
+      <x:c r="A49" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:3">
+      <x:c r="A50" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:3">
+      <x:c r="A51" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:3">
+      <x:c r="A52" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:3">
+      <x:c r="A53" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:3">
+      <x:c r="A54" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:3">
+      <x:c r="A55" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:3">
+      <x:c r="A56" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:3">
+      <x:c r="A57" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:3">
+      <x:c r="A58" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:3">
+      <x:c r="A59" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:3">
+      <x:c r="A60" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:3">
+      <x:c r="A61" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:3">
+      <x:c r="A62" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:3">
+      <x:c r="A63" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:3">
+      <x:c r="A64" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:3">
+      <x:c r="A65" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:3">
+      <x:c r="A66" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:3">
+      <x:c r="A67" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:3">
+      <x:c r="A68" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:3">
+      <x:c r="A69" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:3">
+      <x:c r="A70" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:3">
+      <x:c r="A71" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:3">
+      <x:c r="A72" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:3">
+      <x:c r="A73" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:3">
+      <x:c r="A74" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:3">
+      <x:c r="A75" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:3">
+      <x:c r="A76" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:3">
+      <x:c r="A77" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:3">
+      <x:c r="A78" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:3">
+      <x:c r="A79" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:3">
+      <x:c r="A80" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:3">
+      <x:c r="A81" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:3">
+      <x:c r="A82" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:3">
+      <x:c r="A83" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:3">
+      <x:c r="A84" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:3">
+      <x:c r="A85" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:3">
+      <x:c r="A86" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:3">
+      <x:c r="A87" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:3">
+      <x:c r="A88" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:3">
+      <x:c r="A89" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:3">
+      <x:c r="A90" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:3">
+      <x:c r="A91" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:3">
+      <x:c r="A92" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:3">
+      <x:c r="A93" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:3">
+      <x:c r="A94" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:3">
+      <x:c r="A95" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:3">
+      <x:c r="A96" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:3">
+      <x:c r="A97" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:3">
+      <x:c r="A98" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:3">
+      <x:c r="A99" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:3">
+      <x:c r="A100" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:3">
+      <x:c r="A101" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:3">
+      <x:c r="A102" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:3">
+      <x:c r="A103" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:3">
+      <x:c r="A104" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C104" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:3">
+      <x:c r="A105" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:3">
+      <x:c r="A106" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:3">
+      <x:c r="A107" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:3">
+      <x:c r="A108" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:3">
+      <x:c r="A109" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:3">
+      <x:c r="A110" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:3">
+      <x:c r="A111" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:3">
+      <x:c r="A112" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:3">
+      <x:c r="A113" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:3">
+      <x:c r="A114" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C114" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:3">
+      <x:c r="A115" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:3">
+      <x:c r="A116" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:3">
+      <x:c r="A117" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:3">
+      <x:c r="A118" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:3">
+      <x:c r="A119" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:3">
+      <x:c r="A120" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:3">
+      <x:c r="A121" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:3">
+      <x:c r="A122" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:3">
+      <x:c r="A123" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:3">
+      <x:c r="A124" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:3">
+      <x:c r="A125" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:3">
+      <x:c r="A126" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:3">
+      <x:c r="A127" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:3">
+      <x:c r="A128" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:3">
+      <x:c r="A129" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:3">
+      <x:c r="A130" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:3">
+      <x:c r="A131" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:3">
+      <x:c r="A132" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:3">
+      <x:c r="A133" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:3">
+      <x:c r="A134" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:3">
+      <x:c r="A135" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:3">
+      <x:c r="A136" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:3">
+      <x:c r="A137" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:3">
+      <x:c r="A138" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:3">
+      <x:c r="A139" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:3">
+      <x:c r="A140" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:3">
+      <x:c r="A141" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:3">
+      <x:c r="A142" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:3">
+      <x:c r="A143" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:3">
+      <x:c r="A144" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:3">
+      <x:c r="A145" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:3">
+      <x:c r="A146" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:3">
+      <x:c r="A147" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:3">
+      <x:c r="A148" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:3">
+      <x:c r="A149" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:3">
+      <x:c r="A150" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:3">
+      <x:c r="A151" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:3">
+      <x:c r="A152" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:3">
+      <x:c r="A153" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:3">
+      <x:c r="A154" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:3">
+      <x:c r="A155" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:3">
+      <x:c r="A156" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:3">
+      <x:c r="A157" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:3">
+      <x:c r="A158" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:3">
+      <x:c r="A159" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:3">
+      <x:c r="A160" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:3">
+      <x:c r="A161" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:3">
+      <x:c r="A162" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:3">
+      <x:c r="A163" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:3">
+      <x:c r="A164" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:3">
+      <x:c r="A165" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:3">
+      <x:c r="A166" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:3">
+      <x:c r="A167" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:3">
+      <x:c r="A168" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:3">
+      <x:c r="A169" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:3">
+      <x:c r="A170" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:3">
+      <x:c r="A171" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:3">
+      <x:c r="A172" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:3">
+      <x:c r="A173" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:3">
+      <x:c r="A174" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C174" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:3">
+      <x:c r="A175" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C175" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:3">
+      <x:c r="A176" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C176" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:3">
+      <x:c r="A177" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C177" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:3">
+      <x:c r="A178" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C178" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:3">
+      <x:c r="A179" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C179" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:3">
+      <x:c r="A180" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B180" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C180" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:3">
+      <x:c r="A181" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B181" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C181" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:3">
+      <x:c r="A182" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C182" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:3">
+      <x:c r="A183" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C183" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:3">
+      <x:c r="A184" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C184" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:3">
+      <x:c r="A185" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C185" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:3">
+      <x:c r="A186" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C186" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:3">
+      <x:c r="A187" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C187" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:3">
+      <x:c r="A188" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B188" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C188" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:3">
+      <x:c r="A189" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C189" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:3">
+      <x:c r="A190" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C190" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:3">
+      <x:c r="A191" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C191" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:3">
+      <x:c r="A192" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C192" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:3">
+      <x:c r="A193" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C193" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:3">
+      <x:c r="A194" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C194" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:3">
+      <x:c r="A195" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C195" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:3">
+      <x:c r="A196" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C196" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:3">
+      <x:c r="A197" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B197" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C197" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:3">
+      <x:c r="A198" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B198" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C198" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:3">
+      <x:c r="A199" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B199" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C199" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:3">
+      <x:c r="A200" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B200" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C200" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:3">
+      <x:c r="A201" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B201" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C201" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:3">
+      <x:c r="A202" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B202" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C202" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" spans="1:3">
+      <x:c r="A203" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B203" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C203" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:3">
+      <x:c r="A204" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B204" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C204" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:3">
+      <x:c r="A205" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B205" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C205" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:3">
+      <x:c r="A206" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B206" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C206" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" spans="1:3">
+      <x:c r="A207" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B207" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C207" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:3">
+      <x:c r="A208" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B208" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C208" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:3">
+      <x:c r="A209" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B209" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C209" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" spans="1:3">
+      <x:c r="A210" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B210" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C210" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" spans="1:3">
+      <x:c r="A211" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B211" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C211" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:3">
+      <x:c r="A212" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B212" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C212" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" spans="1:3">
+      <x:c r="A213" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B213" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C213" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:3">
+      <x:c r="A214" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B214" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C214" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:3">
+      <x:c r="A215" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B215" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C215" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" spans="1:3">
+      <x:c r="A216" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="B216" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C216" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:3">
+      <x:c r="A217" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B217" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C217" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" spans="1:3">
+      <x:c r="A218" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B218" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C218" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" spans="1:3">
+      <x:c r="A219" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="B219" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C219" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" spans="1:3">
+      <x:c r="A220" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="B220" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C220" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" spans="1:3">
+      <x:c r="A221" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B221" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C221" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" spans="1:3">
+      <x:c r="A222" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B222" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C222" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" spans="1:3">
+      <x:c r="A223" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="B223" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C223" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" spans="1:3">
+      <x:c r="A224" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B224" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C224" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" spans="1:3">
+      <x:c r="A225" s="0" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B225" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C225" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" spans="1:3">
+      <x:c r="A226" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B226" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C226" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" spans="1:3">
+      <x:c r="A227" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B227" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C227" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" spans="1:3">
+      <x:c r="A228" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B228" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C228" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" spans="1:3">
+      <x:c r="A229" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="B229" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C229" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" spans="1:3">
+      <x:c r="A230" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B230" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C230" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" spans="1:3">
+      <x:c r="A231" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="B231" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C231" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" spans="1:3">
+      <x:c r="A232" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B232" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C232" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" spans="1:3">
+      <x:c r="A233" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B233" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C233" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" spans="1:3">
+      <x:c r="A234" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="B234" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C234" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" spans="1:3">
+      <x:c r="A235" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="B235" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C235" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" spans="1:3">
+      <x:c r="A236" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B236" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C236" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" spans="1:3">
+      <x:c r="A237" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="B237" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C237" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" spans="1:3">
+      <x:c r="A238" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B238" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C238" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" spans="1:3">
+      <x:c r="A239" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B239" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C239" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" spans="1:3">
+      <x:c r="A240" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="B240" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C240" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" spans="1:3">
+      <x:c r="A241" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="B241" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C241" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" spans="1:3">
+      <x:c r="A242" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B242" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C242" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" spans="1:3">
+      <x:c r="A243" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="B243" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C243" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" spans="1:3">
+      <x:c r="A244" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B244" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C244" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" spans="1:3">
+      <x:c r="A245" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="B245" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C245" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" spans="1:3">
+      <x:c r="A246" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B246" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C246" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" spans="1:3">
+      <x:c r="A247" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="B247" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C247" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" spans="1:3">
+      <x:c r="A248" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B248" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C248" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" spans="1:3">
+      <x:c r="A249" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="B249" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C249" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" spans="1:3">
+      <x:c r="A250" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B250" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C250" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" spans="1:3">
+      <x:c r="A251" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="B251" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C251" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" spans="1:3">
+      <x:c r="A252" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B252" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C252" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" spans="1:3">
+      <x:c r="A253" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="B253" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C253" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" spans="1:3">
+      <x:c r="A254" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B254" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C254" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" spans="1:3">
+      <x:c r="A255" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="B255" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C255" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" spans="1:3">
+      <x:c r="A256" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B256" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C256" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" spans="1:3">
+      <x:c r="A257" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B257" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C257" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" spans="1:3">
+      <x:c r="A258" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="B258" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C258" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" spans="1:3">
+      <x:c r="A259" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B259" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C259" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" spans="1:3">
+      <x:c r="A260" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B260" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C260" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" spans="1:3">
+      <x:c r="A261" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B261" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C261" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" spans="1:3">
+      <x:c r="A262" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="B262" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C262" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" spans="1:3">
+      <x:c r="A263" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="B263" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C263" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" spans="1:3">
+      <x:c r="A264" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="B264" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C264" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" spans="1:3">
+      <x:c r="A265" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B265" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C265" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" spans="1:3">
+      <x:c r="A266" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="B266" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C266" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" spans="1:3">
+      <x:c r="A267" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="B267" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C267" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" spans="1:3">
+      <x:c r="A268" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="B268" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C268" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" spans="1:3">
+      <x:c r="A269" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="B269" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C269" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" spans="1:3">
+      <x:c r="A270" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="B270" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C270" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" spans="1:3">
+      <x:c r="A271" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="B271" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C271" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" spans="1:3">
+      <x:c r="A272" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="B272" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C272" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" spans="1:3">
+      <x:c r="A273" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="B273" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C273" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" spans="1:3">
+      <x:c r="A274" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B274" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C274" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" spans="1:3">
+      <x:c r="A275" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="B275" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C275" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" spans="1:3">
+      <x:c r="A276" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="B276" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C276" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" spans="1:3">
+      <x:c r="A277" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B277" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C277" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" spans="1:3">
+      <x:c r="A278" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B278" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C278" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" spans="1:3">
+      <x:c r="A279" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="B279" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C279" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" spans="1:3">
+      <x:c r="A280" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B280" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C280" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" spans="1:3">
+      <x:c r="A281" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B281" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C281" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" spans="1:3">
+      <x:c r="A282" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B282" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C282" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" spans="1:3">
+      <x:c r="A283" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B283" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C283" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" spans="1:3">
+      <x:c r="A284" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B284" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C284" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" spans="1:3">
+      <x:c r="A285" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="B285" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C285" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" spans="1:3">
+      <x:c r="A286" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B286" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C286" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" spans="1:3">
+      <x:c r="A287" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="B287" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C287" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" spans="1:3">
+      <x:c r="A288" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B288" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C288" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" spans="1:3">
+      <x:c r="A289" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B289" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C289" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" spans="1:3">
+      <x:c r="A290" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="B290" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C290" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" spans="1:3">
+      <x:c r="A291" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="B291" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C291" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" spans="1:3">
+      <x:c r="A292" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B292" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C292" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" spans="1:3">
+      <x:c r="A293" s="0" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="B293" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C293" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" spans="1:3">
+      <x:c r="A294" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="B294" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C294" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" spans="1:3">
+      <x:c r="A295" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B295" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C295" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" spans="1:3">
+      <x:c r="A296" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B296" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C296" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" spans="1:3">
+      <x:c r="A297" s="0" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="B297" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C297" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" spans="1:3">
+      <x:c r="A298" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B298" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C298" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" spans="1:3">
+      <x:c r="A299" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="B299" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C299" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" spans="1:3">
+      <x:c r="A300" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B300" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C300" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" spans="1:3">
+      <x:c r="A301" s="0" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B301" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C301" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" spans="1:3">
+      <x:c r="A302" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B302" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C302" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" spans="1:3">
+      <x:c r="A303" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="B303" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C303" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" spans="1:3">
+      <x:c r="A304" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B304" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C304" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" spans="1:3">
+      <x:c r="A305" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="B305" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C305" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" spans="1:3">
+      <x:c r="A306" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B306" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C306" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" spans="1:3">
+      <x:c r="A307" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B307" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C307" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" spans="1:3">
+      <x:c r="A308" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B308" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C308" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" spans="1:3">
+      <x:c r="A309" s="0" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="B309" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C309" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" spans="1:3">
+      <x:c r="A310" s="0" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B310" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C310" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" spans="1:3">
+      <x:c r="A311" s="0" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="B311" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C311" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" spans="1:3">
+      <x:c r="A312" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B312" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C312" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" spans="1:3">
+      <x:c r="A313" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B313" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C313" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" spans="1:3">
+      <x:c r="A314" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="B314" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C314" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" spans="1:3">
+      <x:c r="A315" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B315" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C315" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" spans="1:3">
+      <x:c r="A316" s="0" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B316" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C316" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" spans="1:3">
+      <x:c r="A317" s="0" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B317" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C317" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" spans="1:3">
+      <x:c r="A318" s="0" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B318" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C318" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" spans="1:3">
+      <x:c r="A319" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B319" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C319" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" spans="1:3">
+      <x:c r="A320" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B320" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C320" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" spans="1:3">
+      <x:c r="A321" s="0" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="B321" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C321" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" spans="1:3">
+      <x:c r="A322" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B322" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C322" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" spans="1:3">
+      <x:c r="A323" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B323" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C323" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" spans="1:3">
+      <x:c r="A324" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="B324" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C324" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" spans="1:3">
+      <x:c r="A325" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B325" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C325" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" spans="1:3">
+      <x:c r="A326" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B326" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C326" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" spans="1:3">
+      <x:c r="A327" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B327" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C327" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" spans="1:3">
+      <x:c r="A328" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B328" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C328" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" spans="1:3">
+      <x:c r="A329" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B329" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C329" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" spans="1:3">
+      <x:c r="A330" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="B330" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C330" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" spans="1:3">
+      <x:c r="A331" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B331" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C331" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" spans="1:3">
+      <x:c r="A332" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B332" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C332" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" spans="1:3">
+      <x:c r="A333" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="B333" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C333" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" spans="1:3">
+      <x:c r="A334" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B334" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C334" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" spans="1:3">
+      <x:c r="A335" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="B335" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C335" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" spans="1:3">
+      <x:c r="A336" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B336" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C336" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" spans="1:3">
+      <x:c r="A337" s="0" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="B337" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C337" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338" spans="1:3">
+      <x:c r="A338" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B338" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C338" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" spans="1:3">
+      <x:c r="A339" s="0" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B339" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C339" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" spans="1:3">
+      <x:c r="A340" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B340" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C340" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341" spans="1:3">
+      <x:c r="A341" s="0" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B341" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C341" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" spans="1:3">
+      <x:c r="A342" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="B342" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C342" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" spans="1:3">
+      <x:c r="A343" s="0" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="B343" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C343" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" spans="1:3">
+      <x:c r="A344" s="0" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="B344" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C344" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" spans="1:3">
+      <x:c r="A345" s="0" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="B345" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C345" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" spans="1:3">
+      <x:c r="A346" s="0" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="B346" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C346" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" spans="1:3">
+      <x:c r="A347" s="0" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B347" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C347" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" spans="1:3">
+      <x:c r="A348" s="0" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="B348" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C348" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" spans="1:3">
+      <x:c r="A349" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="B349" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C349" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" spans="1:3">
+      <x:c r="A350" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="B350" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C350" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" spans="1:3">
+      <x:c r="A351" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="B351" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C351" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" spans="1:3">
+      <x:c r="A352" s="0" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="B352" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C352" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" spans="1:3">
+      <x:c r="A353" s="0" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="B353" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C353" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" spans="1:3">
+      <x:c r="A354" s="0" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="B354" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C354" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" spans="1:3">
+      <x:c r="A355" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="B355" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C355" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" spans="1:3">
+      <x:c r="A356" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="B356" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C356" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" spans="1:3">
+      <x:c r="A357" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="B357" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C357" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" spans="1:3">
+      <x:c r="A358" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="B358" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C358" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" spans="1:3">
+      <x:c r="A359" s="0" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="B359" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C359" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" spans="1:3">
+      <x:c r="A360" s="0" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="B360" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C360" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" spans="1:3">
+      <x:c r="A361" s="0" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="B361" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C361" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" spans="1:3">
+      <x:c r="A362" s="0" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="B362" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C362" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" spans="1:3">
+      <x:c r="A363" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="B363" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C363" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364" spans="1:3">
+      <x:c r="A364" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="B364" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C364" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365" spans="1:3">
+      <x:c r="A365" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B365" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C365" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366" spans="1:3">
+      <x:c r="A366" s="0" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="B366" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C366" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367" spans="1:3">
+      <x:c r="A367" s="0" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="B367" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C367" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368" spans="1:3">
+      <x:c r="A368" s="0" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="B368" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C368" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369" spans="1:3">
+      <x:c r="A369" s="0" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="B369" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C369" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370" spans="1:3">
+      <x:c r="A370" s="0" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="B370" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C370" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" spans="1:3">
+      <x:c r="A371" s="0" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="B371" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C371" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" spans="1:3">
+      <x:c r="A372" s="0" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="B372" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C372" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" spans="1:3">
+      <x:c r="A373" s="0" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="B373" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C373" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" spans="1:3">
+      <x:c r="A374" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="B374" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C374" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" spans="1:3">
+      <x:c r="A375" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="B375" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C375" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" spans="1:3">
+      <x:c r="A376" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="B376" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C376" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" spans="1:3">
+      <x:c r="A377" s="0" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="B377" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C377" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" spans="1:3">
+      <x:c r="A378" s="0" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="B378" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C378" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" spans="1:3">
+      <x:c r="A379" s="0" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="B379" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C379" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" spans="1:3">
+      <x:c r="A380" s="0" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="B380" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C380" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" spans="1:3">
+      <x:c r="A381" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B381" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C381" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" spans="1:3">
+      <x:c r="A382" s="0" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="B382" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C382" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" spans="1:3">
+      <x:c r="A383" s="0" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B383" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C383" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" spans="1:3">
+      <x:c r="A384" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="B384" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C384" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" spans="1:3">
+      <x:c r="A385" s="0" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="B385" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C385" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" spans="1:3">
+      <x:c r="A386" s="0" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B386" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C386" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" spans="1:3">
+      <x:c r="A387" s="0" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="B387" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C387" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" spans="1:3">
+      <x:c r="A388" s="0" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="B388" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C388" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" spans="1:3">
+      <x:c r="A389" s="0" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="B389" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C389" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" spans="1:3">
+      <x:c r="A390" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="B390" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C390" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" spans="1:3">
+      <x:c r="A391" s="0" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="B391" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C391" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" spans="1:3">
+      <x:c r="A392" s="0" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="B392" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C392" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" spans="1:3">
+      <x:c r="A393" s="0" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="B393" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C393" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" spans="1:3">
+      <x:c r="A394" s="0" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="B394" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C394" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" spans="1:3">
+      <x:c r="A395" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="B395" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C395" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" spans="1:3">
+      <x:c r="A396" s="0" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B396" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C396" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" spans="1:3">
+      <x:c r="A397" s="0" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="B397" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C397" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" spans="1:3">
+      <x:c r="A398" s="0" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="B398" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C398" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" spans="1:3">
+      <x:c r="A399" s="0" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="B399" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C399" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" spans="1:3">
+      <x:c r="A400" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="B400" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C400" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" spans="1:3">
+      <x:c r="A401" s="0" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B401" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C401" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" spans="1:3">
+      <x:c r="A402" s="0" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="B402" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C402" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" spans="1:3">
+      <x:c r="A403" s="0" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B403" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C403" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" spans="1:3">
+      <x:c r="A404" s="0" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="B404" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C404" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" spans="1:3">
+      <x:c r="A405" s="0" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B405" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C405" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" spans="1:3">
+      <x:c r="A406" s="0" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="B406" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C406" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" spans="1:3">
+      <x:c r="A407" s="0" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="B407" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C407" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" spans="1:3">
+      <x:c r="A408" s="0" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B408" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C408" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" spans="1:3">
+      <x:c r="A409" s="0" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="B409" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C409" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" spans="1:3">
+      <x:c r="A410" s="0" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="B410" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C410" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" spans="1:3">
+      <x:c r="A411" s="0" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="B411" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C411" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" spans="1:3">
+      <x:c r="A412" s="0" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="B412" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C412" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" spans="1:3">
+      <x:c r="A413" s="0" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="B413" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C413" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" spans="1:3">
+      <x:c r="A414" s="0" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="B414" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C414" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" spans="1:3">
+      <x:c r="A415" s="0" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="B415" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C415" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" spans="1:3">
+      <x:c r="A416" s="0" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="B416" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C416" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" spans="1:3">
+      <x:c r="A417" s="0" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="B417" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C417" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" spans="1:3">
+      <x:c r="A418" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="B418" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C418" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" spans="1:3">
+      <x:c r="A419" s="0" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="B419" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C419" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" spans="1:3">
+      <x:c r="A420" s="0" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="B420" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C420" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" spans="1:3">
+      <x:c r="A421" s="0" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B421" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C421" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" spans="1:3">
+      <x:c r="A422" s="0" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="B422" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C422" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" spans="1:3">
+      <x:c r="A423" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="B423" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C423" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" spans="1:3">
+      <x:c r="A424" s="0" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="B424" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C424" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" spans="1:3">
+      <x:c r="A425" s="0" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="B425" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C425" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" spans="1:3">
+      <x:c r="A426" s="0" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="B426" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C426" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" spans="1:3">
+      <x:c r="A427" s="0" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="B427" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C427" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" spans="1:3">
+      <x:c r="A428" s="0" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B428" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C428" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" spans="1:3">
+      <x:c r="A429" s="0" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="B429" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C429" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" spans="1:3">
+      <x:c r="A430" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="B430" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C430" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" spans="1:3">
+      <x:c r="A431" s="0" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B431" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C431" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" spans="1:3">
+      <x:c r="A432" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="B432" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C432" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" spans="1:3">
+      <x:c r="A433" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="B433" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C433" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" spans="1:3">
+      <x:c r="A434" s="0" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="B434" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C434" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" spans="1:3">
+      <x:c r="A435" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="B435" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C435" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" spans="1:3">
+      <x:c r="A436" s="0" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="B436" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C436" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" spans="1:3">
+      <x:c r="A437" s="0" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="B437" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C437" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" spans="1:3">
+      <x:c r="A438" s="0" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="B438" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C438" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" spans="1:3">
+      <x:c r="A439" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="B439" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C439" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" spans="1:3">
+      <x:c r="A440" s="0" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="B440" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C440" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" spans="1:3">
+      <x:c r="A441" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="B441" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C441" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" spans="1:3">
+      <x:c r="A442" s="0" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="B442" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C442" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443" spans="1:3">
+      <x:c r="A443" s="0" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="B443" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C443" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" spans="1:3">
+      <x:c r="A444" s="0" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="B444" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C444" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445" spans="1:3">
+      <x:c r="A445" s="0" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="B445" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C445" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" spans="1:3">
+      <x:c r="A446" s="0" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="B446" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C446" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447" spans="1:3">
+      <x:c r="A447" s="0" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="B447" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C447" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448" spans="1:3">
+      <x:c r="A448" s="0" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B448" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C448" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449" spans="1:3">
+      <x:c r="A449" s="0" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B449" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C449" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450" spans="1:3">
+      <x:c r="A450" s="0" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B450" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C450" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451" spans="1:3">
+      <x:c r="A451" s="0" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B451" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C451" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452" spans="1:3">
+      <x:c r="A452" s="0" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="B452" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C452" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453" spans="1:3">
+      <x:c r="A453" s="0" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="B453" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C453" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454" spans="1:3">
+      <x:c r="A454" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B454" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C454" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455" spans="1:3">
+      <x:c r="A455" s="0" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="B455" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C455" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456" spans="1:3">
+      <x:c r="A456" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B456" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C456" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457" spans="1:3">
+      <x:c r="A457" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B457" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C457" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458" spans="1:3">
+      <x:c r="A458" s="0" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="B458" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C458" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459" spans="1:3">
+      <x:c r="A459" s="0" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="B459" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C459" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460" spans="1:3">
+      <x:c r="A460" s="0" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B460" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C460" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461" spans="1:3">
+      <x:c r="A461" s="0" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="B461" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C461" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462" spans="1:3">
+      <x:c r="A462" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="B462" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C462" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463" spans="1:3">
+      <x:c r="A463" s="0" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B463" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C463" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464" spans="1:3">
+      <x:c r="A464" s="0" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="B464" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C464" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465" spans="1:3">
+      <x:c r="A465" s="0" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="B465" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C465" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466" spans="1:3">
+      <x:c r="A466" s="0" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="B466" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C466" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467" spans="1:3">
+      <x:c r="A467" s="0" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="B467" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C467" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468" spans="1:3">
+      <x:c r="A468" s="0" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="B468" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C468" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469" spans="1:3">
+      <x:c r="A469" s="0" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="B469" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C469" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470" spans="1:3">
+      <x:c r="A470" s="0" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B470" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C470" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471" spans="1:3">
+      <x:c r="A471" s="0" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="B471" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C471" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472" spans="1:3">
+      <x:c r="A472" s="0" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="B472" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C472" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473" spans="1:3">
+      <x:c r="A473" s="0" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="B473" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C473" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474" spans="1:3">
+      <x:c r="A474" s="0" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="B474" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C474" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475" spans="1:3">
+      <x:c r="A475" s="0" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B475" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C475" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476" spans="1:3">
+      <x:c r="A476" s="0" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B476" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C476" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477" spans="1:3">
+      <x:c r="A477" s="0" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="B477" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C477" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478" spans="1:3">
+      <x:c r="A478" s="0" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="B478" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C478" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479" spans="1:3">
+      <x:c r="A479" s="0" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B479" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C479" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480" spans="1:3">
+      <x:c r="A480" s="0" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="B480" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C480" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481" spans="1:3">
+      <x:c r="A481" s="0" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="B481" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C481" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482" spans="1:3">
+      <x:c r="A482" s="0" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B482" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C482" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483" spans="1:3">
+      <x:c r="A483" s="0" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="B483" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C483" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484" spans="1:3">
+      <x:c r="A484" s="0" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="B484" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C484" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485" spans="1:3">
+      <x:c r="A485" s="0" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B485" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C485" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486" spans="1:3">
+      <x:c r="A486" s="0" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="B486" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C486" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487" spans="1:3">
+      <x:c r="A487" s="0" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="B487" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C487" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488" spans="1:3">
+      <x:c r="A488" s="0" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B488" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C488" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489" spans="1:3">
+      <x:c r="A489" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="B489" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C489" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490" spans="1:3">
+      <x:c r="A490" s="0" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="B490" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C490" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491" spans="1:3">
+      <x:c r="A491" s="0" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B491" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C491" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492" spans="1:3">
+      <x:c r="A492" s="0" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="B492" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C492" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493" spans="1:3">
+      <x:c r="A493" s="0" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="B493" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C493" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494" spans="1:3">
+      <x:c r="A494" s="0" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="B494" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C494" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495" spans="1:3">
+      <x:c r="A495" s="0" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="B495" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C495" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" spans="1:3">
+      <x:c r="A496" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="B496" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C496" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497" spans="1:3">
+      <x:c r="A497" s="0" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="B497" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C497" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498" spans="1:3">
+      <x:c r="A498" s="0" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="B498" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C498" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499" spans="1:3">
+      <x:c r="A499" s="0" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="B499" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C499" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" spans="1:3">
+      <x:c r="A500" s="0" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="B500" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C500" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501" spans="1:3">
+      <x:c r="A501" s="0" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="B501" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C501" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" spans="1:3">
+      <x:c r="A502" s="0" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="B502" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C502" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503" spans="1:3">
+      <x:c r="A503" s="0" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="B503" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C503" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504" spans="1:3">
+      <x:c r="A504" s="0" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="B504" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C504" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505" spans="1:3">
+      <x:c r="A505" s="0" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="B505" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C505" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506" spans="1:3">
+      <x:c r="A506" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="B506" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C506" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507" spans="1:3">
+      <x:c r="A507" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="B507" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C507" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" spans="1:3">
+      <x:c r="A508" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="B508" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C508" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509" spans="1:3">
+      <x:c r="A509" s="0" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="B509" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C509" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510" spans="1:3">
+      <x:c r="A510" s="0" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="B510" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C510" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511" spans="1:3">
+      <x:c r="A511" s="0" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="B511" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C511" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512" spans="1:3">
+      <x:c r="A512" s="0" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="B512" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C512" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513" spans="1:3">
+      <x:c r="A513" s="0" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="B513" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C513" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514" spans="1:3">
+      <x:c r="A514" s="0" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B514" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C514" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515" spans="1:3">
+      <x:c r="A515" s="0" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="B515" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C515" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516" spans="1:3">
+      <x:c r="A516" s="0" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="B516" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C516" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517" spans="1:3">
+      <x:c r="A517" s="0" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="B517" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C517" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518" spans="1:3">
+      <x:c r="A518" s="0" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="B518" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C518" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519" spans="1:3">
+      <x:c r="A519" s="0" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="B519" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C519" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520" spans="1:3">
+      <x:c r="A520" s="0" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="B520" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C520" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521" spans="1:3">
+      <x:c r="A521" s="0" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="B521" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C521" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522" spans="1:3">
+      <x:c r="A522" s="0" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="B522" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C522" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523" spans="1:3">
+      <x:c r="A523" s="0" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="B523" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C523" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524" spans="1:3">
+      <x:c r="A524" s="0" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="B524" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C524" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525" spans="1:3">
+      <x:c r="A525" s="0" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="B525" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C525" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526" spans="1:3">
+      <x:c r="A526" s="0" t="s">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="B526" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C526" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527" spans="1:3">
+      <x:c r="A527" s="0" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="B527" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C527" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528" spans="1:3">
+      <x:c r="A528" s="0" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="B528" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C528" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529" spans="1:3">
+      <x:c r="A529" s="0" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="B529" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C529" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530" spans="1:3">
+      <x:c r="A530" s="0" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="B530" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C530" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531" spans="1:3">
+      <x:c r="A531" s="0" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B531" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C531" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532" spans="1:3">
+      <x:c r="A532" s="0" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="B532" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C532" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533" spans="1:3">
+      <x:c r="A533" s="0" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="B533" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C533" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534" spans="1:3">
+      <x:c r="A534" s="0" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="B534" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C534" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535" spans="1:3">
+      <x:c r="A535" s="0" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="B535" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C535" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536" spans="1:3">
+      <x:c r="A536" s="0" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="B536" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C536" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537" spans="1:3">
+      <x:c r="A537" s="0" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B537" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C537" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538" spans="1:3">
+      <x:c r="A538" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="B538" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C538" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539" spans="1:3">
+      <x:c r="A539" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="B539" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C539" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540" spans="1:3">
+      <x:c r="A540" s="0" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="B540" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C540" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541" spans="1:3">
+      <x:c r="A541" s="0" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="B541" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C541" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542" spans="1:3">
+      <x:c r="A542" s="0" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="B542" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C542" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543" spans="1:3">
+      <x:c r="A543" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="B543" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C543" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544" spans="1:3">
+      <x:c r="A544" s="0" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="B544" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C544" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545" spans="1:3">
+      <x:c r="A545" s="0" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="B545" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C545" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546" spans="1:3">
+      <x:c r="A546" s="0" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="B546" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C546" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547" spans="1:3">
+      <x:c r="A547" s="0" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="B547" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C547" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548" spans="1:3">
+      <x:c r="A548" s="0" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="B548" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C548" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549" spans="1:3">
+      <x:c r="A549" s="0" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="B549" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C549" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550" spans="1:3">
+      <x:c r="A550" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="B550" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C550" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551" spans="1:3">
+      <x:c r="A551" s="0" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="B551" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C551" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552" spans="1:3">
+      <x:c r="A552" s="0" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="B552" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C552" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553" spans="1:3">
+      <x:c r="A553" s="0" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="B553" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C553" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554" spans="1:3">
+      <x:c r="A554" s="0" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="B554" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C554" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555" spans="1:3">
+      <x:c r="A555" s="0" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="B555" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C555" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556" spans="1:3">
+      <x:c r="A556" s="0" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="B556" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C556" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557" spans="1:3">
+      <x:c r="A557" s="0" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="B557" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C557" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558" spans="1:3">
+      <x:c r="A558" s="0" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="B558" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C558" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559" spans="1:3">
+      <x:c r="A559" s="0" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="B559" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C559" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560" spans="1:3">
+      <x:c r="A560" s="0" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="B560" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C560" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561" spans="1:3">
+      <x:c r="A561" s="0" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B561" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C561" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562" spans="1:3">
+      <x:c r="A562" s="0" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="B562" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C562" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563" spans="1:3">
+      <x:c r="A563" s="0" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="B563" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C563" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564" spans="1:3">
+      <x:c r="A564" s="0" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="B564" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C564" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565" spans="1:3">
+      <x:c r="A565" s="0" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="B565" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C565" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566" spans="1:3">
+      <x:c r="A566" s="0" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="B566" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C566" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567" spans="1:3">
+      <x:c r="A567" s="0" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="B567" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C567" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568" spans="1:3">
+      <x:c r="A568" s="0" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="B568" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C568" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569" spans="1:3">
+      <x:c r="A569" s="0" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="B569" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C569" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570" spans="1:3">
+      <x:c r="A570" s="0" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="B570" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C570" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571" spans="1:3">
+      <x:c r="A571" s="0" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="B571" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C571" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572" spans="1:3">
+      <x:c r="A572" s="0" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="B572" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C572" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573" spans="1:3">
+      <x:c r="A573" s="0" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="B573" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C573" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="574" spans="1:3">
+      <x:c r="A574" s="0" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="B574" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C574" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575" spans="1:3">
+      <x:c r="A575" s="0" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="B575" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C575" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="576" spans="1:3">
+      <x:c r="A576" s="0" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="B576" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C576" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="577" spans="1:3">
+      <x:c r="A577" s="0" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="B577" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C577" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="578" spans="1:3">
+      <x:c r="A578" s="0" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="B578" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C578" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579" spans="1:3">
+      <x:c r="A579" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="B579" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C579" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="580" spans="1:3">
+      <x:c r="A580" s="0" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="B580" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C580" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581" spans="1:3">
+      <x:c r="A581" s="0" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="B581" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C581" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582" spans="1:3">
+      <x:c r="A582" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="B582" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C582" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="583" spans="1:3">
+      <x:c r="A583" s="0" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="B583" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C583" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584" spans="1:3">
+      <x:c r="A584" s="0" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="B584" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C584" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="585" spans="1:3">
+      <x:c r="A585" s="0" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="B585" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C585" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586" spans="1:3">
+      <x:c r="A586" s="0" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="B586" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C586" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587" spans="1:3">
+      <x:c r="A587" s="0" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B587" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C587" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="588" spans="1:3">
+      <x:c r="A588" s="0" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="B588" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C588" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589" spans="1:3">
+      <x:c r="A589" s="0" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="B589" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C589" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="590" spans="1:3">
+      <x:c r="A590" s="0" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="B590" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C590" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591" spans="1:3">
+      <x:c r="A591" s="0" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="B591" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C591" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="592" spans="1:3">
+      <x:c r="A592" s="0" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B592" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C592" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593" spans="1:3">
+      <x:c r="A593" s="0" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="B593" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C593" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594" spans="1:3">
+      <x:c r="A594" s="0" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="B594" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C594" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="595" spans="1:3">
+      <x:c r="A595" s="0" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="B595" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C595" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596" spans="1:3">
+      <x:c r="A596" s="0" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="B596" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C596" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="597" spans="1:3">
+      <x:c r="A597" s="0" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="B597" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C597" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598" spans="1:3">
+      <x:c r="A598" s="0" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="B598" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C598" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="599" spans="1:3">
+      <x:c r="A599" s="0" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="B599" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C599" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600" spans="1:3">
+      <x:c r="A600" s="0" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="B600" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C600" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601" spans="1:3">
+      <x:c r="A601" s="0" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B601" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C601" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="602" spans="1:3">
+      <x:c r="A602" s="0" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="B602" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C602" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603" spans="1:3">
+      <x:c r="A603" s="0" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="B603" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C603" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604" spans="1:3">
+      <x:c r="A604" s="0" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="B604" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C604" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605" spans="1:3">
+      <x:c r="A605" s="0" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="B605" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C605" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606" spans="1:3">
+      <x:c r="A606" s="0" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="B606" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C606" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607" spans="1:3">
+      <x:c r="A607" s="0" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="B607" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C607" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608" spans="1:3">
+      <x:c r="A608" s="0" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="B608" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C608" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609" spans="1:3">
+      <x:c r="A609" s="0" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="B609" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C609" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610" spans="1:3">
+      <x:c r="A610" s="0" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B610" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C610" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611" spans="1:3">
+      <x:c r="A611" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="B611" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C611" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612" spans="1:3">
+      <x:c r="A612" s="0" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="B612" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C612" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613" spans="1:3">
+      <x:c r="A613" s="0" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="B613" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C613" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614" spans="1:3">
+      <x:c r="A614" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="B614" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C614" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615" spans="1:3">
+      <x:c r="A615" s="0" t="s">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="B615" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C615" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616" spans="1:3">
+      <x:c r="A616" s="0" t="s">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="B616" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C616" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617" spans="1:3">
+      <x:c r="A617" s="0" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="B617" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C617" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618" spans="1:3">
+      <x:c r="A618" s="0" t="s">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="B618" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C618" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619" spans="1:3">
+      <x:c r="A619" s="0" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="B619" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C619" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620" spans="1:3">
+      <x:c r="A620" s="0" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="B620" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C620" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621" spans="1:3">
+      <x:c r="A621" s="0" t="s">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="B621" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C621" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622" spans="1:3">
+      <x:c r="A622" s="0" t="s">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="B622" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C622" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623" spans="1:3">
+      <x:c r="A623" s="0" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="B623" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C623" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624" spans="1:3">
+      <x:c r="A624" s="0" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="B624" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C624" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625" spans="1:3">
+      <x:c r="A625" s="0" t="s">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="B625" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C625" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="626" spans="1:3">
+      <x:c r="A626" s="0" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="B626" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C626" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="627" spans="1:3">
+      <x:c r="A627" s="0" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="B627" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C627" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,46 +26,34 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -416,7 +404,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -428,17 +416,6 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -455,7 +432,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C12"/>
+  <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -471,7 +448,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -482,7 +459,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -493,7 +470,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -504,7 +481,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -515,7 +492,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -526,7 +503,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -537,7 +514,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -548,45 +525,12 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:3">
-      <x:c r="A11" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:3">
-      <x:c r="A12" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,21 +26,21 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
@@ -48,9 +48,6 @@
   </x:si>
   <x:si>
     <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>SKYMD</x:t>
@@ -432,7 +429,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C9"/>
+  <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -520,17 +517,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:3">
-      <x:c r="A9" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -35,12 +35,18 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
@@ -51,6 +57,9 @@
   </x:si>
   <x:si>
     <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -401,7 +410,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C1"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -413,6 +422,17 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -429,7 +449,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C8"/>
+  <x:dimension ref="A1:C10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -445,7 +465,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -456,7 +476,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -467,7 +487,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -478,7 +498,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -489,7 +509,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -500,7 +520,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -511,12 +531,34 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:3">
+      <x:c r="A9" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -35,6 +35,9 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
@@ -44,9 +47,6 @@
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
@@ -56,10 +56,7 @@
     <x:t>HUNER</x:t>
   </x:si>
   <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
+    <x:t>KRPLS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -410,7 +407,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -422,17 +419,6 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -465,7 +451,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -476,7 +462,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -487,7 +473,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -498,7 +484,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -509,7 +495,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -520,7 +506,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -531,7 +517,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -542,7 +528,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -553,7 +539,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,37 +26,37 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -407,7 +407,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C1"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -419,6 +419,17 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -435,7 +446,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C10"/>
+  <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -451,7 +462,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -462,7 +473,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -473,7 +484,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -484,7 +495,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -495,7 +506,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -506,7 +517,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -517,7 +528,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -528,23 +539,12 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,34 +26,37 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
+    <x:t>DURDO</x:t>
   </x:si>
   <x:si>
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
+    <x:t>INDES</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
@@ -446,7 +449,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C9"/>
+  <x:dimension ref="A1:C10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -545,6 +548,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>RYGYO</x:t>
+    <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,15 +35,15 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
   </x:si>
   <x:si>
     <x:t>AVGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
@@ -56,7 +56,7 @@
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
-    <x:t>INDES</x:t>
+    <x:t>ISDMR</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
@@ -410,7 +410,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -422,17 +422,6 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -449,7 +438,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C10"/>
+  <x:dimension ref="A1:C11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -465,7 +454,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -476,7 +465,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -487,7 +476,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -498,7 +487,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -509,7 +498,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -520,7 +509,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -531,7 +520,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -542,7 +531,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -553,12 +542,23 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3">
+      <x:c r="A11" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
+      <x:c r="B11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -35,15 +35,9 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALBRK</x:t>
   </x:si>
   <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
@@ -53,13 +47,13 @@
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
     <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -438,7 +432,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C11"/>
+  <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -537,28 +531,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:3">
-      <x:c r="A11" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,13 +26,19 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
+    <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
     <x:t>ALBRK</x:t>
@@ -50,10 +56,28 @@
     <x:t>ENJSA</x:t>
   </x:si>
   <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
     <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -404,7 +428,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C1"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -416,6 +440,17 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -432,7 +467,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C9"/>
+  <x:dimension ref="A1:C16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -448,7 +483,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -459,7 +494,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -470,7 +505,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -481,7 +516,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -492,7 +527,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -503,7 +538,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -514,7 +549,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -525,12 +560,89 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3">
+      <x:c r="A11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:3">
+      <x:c r="A12" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,55 +26,37 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
     <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
     <x:t>VAKBN</x:t>
@@ -428,7 +410,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -440,17 +422,6 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -467,7 +438,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C16"/>
+  <x:dimension ref="A1:C11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -483,7 +454,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -494,7 +465,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -505,7 +476,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -516,7 +487,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -527,7 +498,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -538,7 +509,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -549,7 +520,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -560,7 +531,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -571,7 +542,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -582,67 +553,12 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:3">
-      <x:c r="A12" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:3">
-      <x:c r="A13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:3">
-      <x:c r="A14" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:3">
-      <x:c r="A15" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:3">
-      <x:c r="A16" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
+    <x:t>VAKBN</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,21 +35,21 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
     <x:t>DURDO</x:t>
   </x:si>
   <x:si>
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>GLYHO</x:t>
   </x:si>
   <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
@@ -59,7 +59,7 @@
     <x:t>ORGE</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKBN</x:t>
+    <x:t>RYGYO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -410,7 +410,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C1"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -422,6 +422,17 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -438,7 +449,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C11"/>
+  <x:dimension ref="A1:C10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -454,7 +465,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -465,7 +476,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -476,7 +487,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -487,7 +498,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -498,7 +509,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -509,7 +520,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -520,7 +531,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -531,7 +542,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -542,23 +553,12 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:3">
-      <x:c r="A11" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,40 +26,43 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
     <x:t>VAKBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -449,7 +452,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C10"/>
+  <x:dimension ref="A1:C11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -559,6 +562,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3">
+      <x:c r="A11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,43 +26,34 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
     <x:t>INDES</x:t>
   </x:si>
   <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKBN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -413,7 +404,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -425,17 +416,6 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -452,7 +432,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C11"/>
+  <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -468,7 +448,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -479,7 +459,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -490,7 +470,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -501,7 +481,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -512,7 +492,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -523,7 +503,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -534,7 +514,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -545,34 +525,12 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:3">
-      <x:c r="A11" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
+    <x:t>GLYHO</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,25 +35,10 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
+    <x:t>RYSAS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -432,7 +417,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C9"/>
+  <x:dimension ref="A1:C4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -476,61 +461,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:3">
-      <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:3">
-      <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:3">
-      <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:3">
-      <x:c r="A9" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>GLYHO</x:t>
+    <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,10 +35,7 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
+    <x:t>SOKM</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -417,7 +414,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C4"/>
+  <x:dimension ref="A1:C3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -450,17 +447,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,13 +26,34 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
+    <x:t>INDES</x:t>
   </x:si>
   <x:si>
     <x:t>SOKM</x:t>
@@ -414,7 +435,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C3"/>
+  <x:dimension ref="A1:C10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -447,6 +468,83 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:3">
+      <x:c r="A5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:3">
+      <x:c r="A6" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:3">
+      <x:c r="A7" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:3">
+      <x:c r="A8" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:3">
+      <x:c r="A9" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
+    <x:t>ENJSA</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,28 +35,10 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
+    <x:t>RYGYO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -435,7 +417,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C10"/>
+  <x:dimension ref="A1:C4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -479,72 +461,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:3">
-      <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:3">
-      <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:3">
-      <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:3">
-      <x:c r="A9" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,19 +26,13 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>ENJSA</x:t>
+    <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
   </x:si>
   <x:si>
     <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -417,7 +411,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C4"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -439,28 +433,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,13 +26,25 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
     <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -411,7 +423,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -433,6 +445,50 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:3">
+      <x:c r="A5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:3">
+      <x:c r="A6" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,22 +26,13 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>DOCO</x:t>
+    <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
   </x:si>
   <x:si>
     <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
     <x:t>RYGYO</x:t>
@@ -395,7 +386,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C1"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -407,6 +398,17 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -423,7 +425,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C6"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -439,56 +441,12 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:3">
-      <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/macd-al.xlsx
+++ b/app/borsa/gosterge-taramalari/data/macd-al.xlsx
@@ -26,16 +26,19 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
     <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -386,7 +389,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -398,17 +401,6 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -425,7 +417,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -441,12 +433,34 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
